--- a/data/trans_dic/P19F$tarde-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,99; 38,7</t>
+          <t>25,03; 37,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,37; 43,07</t>
+          <t>29,74; 44,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,33; 38,48</t>
+          <t>29,28; 38,77</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,75; 37,46</t>
+          <t>26,97; 37,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,26; 43,24</t>
+          <t>32,54; 43,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,09; 38,5</t>
+          <t>31,02; 38,66</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,49; 40,83</t>
+          <t>30,15; 40,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,89; 36,95</t>
+          <t>27,36; 37,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,27; 37,82</t>
+          <t>30,02; 37,7</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,29; 40,34</t>
+          <t>28,92; 39,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,68; 36,04</t>
+          <t>25,75; 36,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,28; 36,47</t>
+          <t>28,9; 36,45</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,62; 33,41</t>
+          <t>21,19; 33,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,87; 39,32</t>
+          <t>26,96; 39,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,72; 34,17</t>
+          <t>26,18; 34,74</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,83; 27,18</t>
+          <t>15,45; 27,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,69; 30,83</t>
+          <t>19,16; 31,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,98; 27,78</t>
+          <t>18,78; 27,94</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,2; 30,77</t>
+          <t>16,41; 29,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,02; 35,93</t>
+          <t>20,36; 35,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,75; 31,26</t>
+          <t>20,76; 31,48</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,74; 32,97</t>
+          <t>28,56; 33,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 34,25</t>
+          <t>29,96; 34,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,6; 32,88</t>
+          <t>29,71; 32,95</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59542; 88640</t>
+          <t>57327; 86786</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52360; 76786</t>
+          <t>53018; 79008</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119460; 156759</t>
+          <t>119251; 157916</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91086; 122953</t>
+          <t>88540; 124260</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87680; 117521</t>
+          <t>88432; 118508</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186536; 231022</t>
+          <t>186107; 231967</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>105975; 141916</t>
+          <t>104789; 141886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87623; 120432</t>
+          <t>89178; 120793</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>203883; 254722</t>
+          <t>202168; 253904</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99449; 136969</t>
+          <t>98174; 135146</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85020; 119301</t>
+          <t>85241; 119815</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>196321; 244548</t>
+          <t>193769; 244439</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50874; 78633</t>
+          <t>49872; 78337</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70610; 103334</t>
+          <t>70864; 102913</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128135; 170203</t>
+          <t>130398; 173061</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25748; 47188</t>
+          <t>26815; 47199</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34546; 56984</t>
+          <t>35414; 57998</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68028; 99551</t>
+          <t>67294; 100132</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20329; 38605</t>
+          <t>20589; 37524</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39499; 67528</t>
+          <t>38273; 67261</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65037; 97967</t>
+          <t>65057; 98646</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>511174; 586444</t>
+          <t>508029; 588603</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>519259; 596831</t>
+          <t>522131; 603307</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1042418; 1157740</t>
+          <t>1046212; 1160166</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$tarde-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,03; 37,89</t>
+          <t>25,58; 37,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,74; 44,32</t>
+          <t>29,55; 43,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,28; 38,77</t>
+          <t>28,78; 38,51</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,97; 37,86</t>
+          <t>27,74; 37,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,54; 43,6</t>
+          <t>32,23; 43,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,02; 38,66</t>
+          <t>31,04; 38,93</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,15; 40,82</t>
+          <t>30,8; 41,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,36; 37,07</t>
+          <t>27,19; 37,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,02; 37,7</t>
+          <t>29,82; 37,4</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,92; 39,81</t>
+          <t>29,12; 39,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,75; 36,19</t>
+          <t>26,05; 35,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,9; 36,45</t>
+          <t>29,15; 36,47</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,19; 33,29</t>
+          <t>21,29; 32,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,96; 39,16</t>
+          <t>27,0; 39,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,18; 34,74</t>
+          <t>25,58; 34,41</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,45; 27,19</t>
+          <t>15,02; 27,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,16; 31,38</t>
+          <t>18,84; 31,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 27,94</t>
+          <t>18,65; 27,95</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,41; 29,91</t>
+          <t>16,63; 30,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,36; 35,79</t>
+          <t>20,99; 36,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,76; 31,48</t>
+          <t>20,51; 31,29</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,09</t>
+          <t>28,43; 33,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,96; 34,62</t>
+          <t>29,82; 34,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,71; 32,95</t>
+          <t>29,95; 33,01</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57327; 86786</t>
+          <t>58591; 86504</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53018; 79008</t>
+          <t>52672; 77755</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119251; 157916</t>
+          <t>117251; 156852</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88540; 124260</t>
+          <t>91058; 123787</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88432; 118508</t>
+          <t>87602; 117553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186107; 231967</t>
+          <t>186246; 233608</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>104789; 141886</t>
+          <t>107061; 144264</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89178; 120793</t>
+          <t>88614; 121138</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>202168; 253904</t>
+          <t>200858; 251910</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98174; 135146</t>
+          <t>98861; 134825</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85241; 119815</t>
+          <t>86228; 118817</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>193769; 244439</t>
+          <t>195496; 244564</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49872; 78337</t>
+          <t>50105; 77575</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70864; 102913</t>
+          <t>70954; 103785</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130398; 173061</t>
+          <t>127449; 171402</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26815; 47199</t>
+          <t>26082; 48110</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35414; 57998</t>
+          <t>34815; 58120</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67294; 100132</t>
+          <t>66848; 100170</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20589; 37524</t>
+          <t>20863; 38555</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38273; 67261</t>
+          <t>39448; 68521</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65057; 98646</t>
+          <t>64283; 98061</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>508029; 588603</t>
+          <t>505745; 589137</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>522131; 603307</t>
+          <t>519547; 596318</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1046212; 1160166</t>
+          <t>1054609; 1162218</t>
         </is>
       </c>
     </row>
